--- a/artfynd/A 45008-2023 artfynd.xlsx
+++ b/artfynd/A 45008-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120290802</v>
+        <v>120290803</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>79527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564039</v>
+        <v>564046</v>
       </c>
       <c r="R2" t="n">
-        <v>7018489</v>
+        <v>7018479</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120290797</v>
+        <v>120290796</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>79489</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>388</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563965</v>
+        <v>563924</v>
       </c>
       <c r="R3" t="n">
-        <v>7018323</v>
+        <v>7018428</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120290796</v>
+        <v>120290802</v>
       </c>
       <c r="B4" t="n">
-        <v>79473</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563924</v>
+        <v>564039</v>
       </c>
       <c r="R4" t="n">
-        <v>7018428</v>
+        <v>7018489</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120290800</v>
+        <v>120290795</v>
       </c>
       <c r="B5" t="n">
-        <v>91005</v>
+        <v>90591</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564059</v>
+        <v>563877</v>
       </c>
       <c r="R5" t="n">
-        <v>7018401</v>
+        <v>7018280</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120290803</v>
+        <v>120290797</v>
       </c>
       <c r="B6" t="n">
-        <v>79511</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564046</v>
+        <v>563965</v>
       </c>
       <c r="R6" t="n">
-        <v>7018479</v>
+        <v>7018323</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120290799</v>
+        <v>120290798</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>79589</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>229748</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564051</v>
+        <v>563983</v>
       </c>
       <c r="R7" t="n">
-        <v>7018386</v>
+        <v>7018470</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120290798</v>
+        <v>120290801</v>
       </c>
       <c r="B8" t="n">
-        <v>79573</v>
+        <v>79658</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229748</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563983</v>
+        <v>564059</v>
       </c>
       <c r="R8" t="n">
-        <v>7018470</v>
+        <v>7018401</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120290801</v>
+        <v>120290800</v>
       </c>
       <c r="B9" t="n">
-        <v>79642</v>
+        <v>91023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120290795</v>
+        <v>120290799</v>
       </c>
       <c r="B10" t="n">
-        <v>90573</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563877</v>
+        <v>564051</v>
       </c>
       <c r="R10" t="n">
-        <v>7018280</v>
+        <v>7018386</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45008-2023 artfynd.xlsx
+++ b/artfynd/A 45008-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120290803</v>
+        <v>120290796</v>
       </c>
       <c r="B2" t="n">
-        <v>79527</v>
+        <v>79489</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564046</v>
+        <v>563924</v>
       </c>
       <c r="R2" t="n">
-        <v>7018479</v>
+        <v>7018428</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120290796</v>
+        <v>120290803</v>
       </c>
       <c r="B3" t="n">
-        <v>79489</v>
+        <v>79527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>388</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563924</v>
+        <v>564046</v>
       </c>
       <c r="R3" t="n">
-        <v>7018428</v>
+        <v>7018479</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120290802</v>
+        <v>120290795</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>90591</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564039</v>
+        <v>563877</v>
       </c>
       <c r="R4" t="n">
-        <v>7018489</v>
+        <v>7018280</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120290795</v>
+        <v>120290797</v>
       </c>
       <c r="B5" t="n">
-        <v>90591</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563877</v>
+        <v>563965</v>
       </c>
       <c r="R5" t="n">
-        <v>7018280</v>
+        <v>7018323</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120290797</v>
+        <v>120290800</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>91023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563965</v>
+        <v>564059</v>
       </c>
       <c r="R6" t="n">
-        <v>7018323</v>
+        <v>7018401</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120290798</v>
+        <v>120290801</v>
       </c>
       <c r="B7" t="n">
-        <v>79589</v>
+        <v>79658</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229748</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563983</v>
+        <v>564059</v>
       </c>
       <c r="R7" t="n">
-        <v>7018470</v>
+        <v>7018401</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120290801</v>
+        <v>120290802</v>
       </c>
       <c r="B8" t="n">
-        <v>79658</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564059</v>
+        <v>564039</v>
       </c>
       <c r="R8" t="n">
-        <v>7018401</v>
+        <v>7018489</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120290800</v>
+        <v>120290798</v>
       </c>
       <c r="B9" t="n">
-        <v>91023</v>
+        <v>79589</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>229748</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564059</v>
+        <v>563983</v>
       </c>
       <c r="R9" t="n">
-        <v>7018401</v>
+        <v>7018470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 45008-2023 artfynd.xlsx
+++ b/artfynd/A 45008-2023 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120290795</v>
+        <v>120290797</v>
       </c>
       <c r="B4" t="n">
-        <v>90591</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563877</v>
+        <v>563965</v>
       </c>
       <c r="R4" t="n">
-        <v>7018280</v>
+        <v>7018323</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120290797</v>
+        <v>120290795</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>90591</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563965</v>
+        <v>563877</v>
       </c>
       <c r="R5" t="n">
-        <v>7018323</v>
+        <v>7018280</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 45008-2023 artfynd.xlsx
+++ b/artfynd/A 45008-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120290803</v>
+        <v>120290802</v>
       </c>
       <c r="B3" t="n">
-        <v>79527</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564046</v>
+        <v>564039</v>
       </c>
       <c r="R3" t="n">
-        <v>7018479</v>
+        <v>7018489</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120290795</v>
+        <v>120290798</v>
       </c>
       <c r="B5" t="n">
-        <v>90591</v>
+        <v>79589</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>229748</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563877</v>
+        <v>563983</v>
       </c>
       <c r="R5" t="n">
-        <v>7018280</v>
+        <v>7018470</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120290800</v>
+        <v>120290801</v>
       </c>
       <c r="B6" t="n">
-        <v>91023</v>
+        <v>79658</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120290801</v>
+        <v>120290803</v>
       </c>
       <c r="B7" t="n">
-        <v>79658</v>
+        <v>79527</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564059</v>
+        <v>564046</v>
       </c>
       <c r="R7" t="n">
-        <v>7018401</v>
+        <v>7018479</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120290802</v>
+        <v>120290799</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564039</v>
+        <v>564051</v>
       </c>
       <c r="R8" t="n">
-        <v>7018489</v>
+        <v>7018386</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120290798</v>
+        <v>120290795</v>
       </c>
       <c r="B9" t="n">
-        <v>79589</v>
+        <v>90591</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229748</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563983</v>
+        <v>563877</v>
       </c>
       <c r="R9" t="n">
-        <v>7018470</v>
+        <v>7018280</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120290799</v>
+        <v>120290800</v>
       </c>
       <c r="B10" t="n">
-        <v>90598</v>
+        <v>91023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564051</v>
+        <v>564059</v>
       </c>
       <c r="R10" t="n">
-        <v>7018386</v>
+        <v>7018401</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45008-2023 artfynd.xlsx
+++ b/artfynd/A 45008-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120290796</v>
+        <v>120290795</v>
       </c>
       <c r="B2" t="n">
-        <v>79489</v>
+        <v>90591</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>388</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563924</v>
+        <v>563877</v>
       </c>
       <c r="R2" t="n">
-        <v>7018428</v>
+        <v>7018280</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120290802</v>
+        <v>120290796</v>
       </c>
       <c r="B3" t="n">
-        <v>79623</v>
+        <v>79489</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564039</v>
+        <v>563924</v>
       </c>
       <c r="R3" t="n">
-        <v>7018489</v>
+        <v>7018428</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120290797</v>
+        <v>120290800</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>91023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563965</v>
+        <v>564059</v>
       </c>
       <c r="R4" t="n">
-        <v>7018323</v>
+        <v>7018401</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120290798</v>
+        <v>120290801</v>
       </c>
       <c r="B5" t="n">
-        <v>79589</v>
+        <v>79658</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229748</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563983</v>
+        <v>564059</v>
       </c>
       <c r="R5" t="n">
-        <v>7018470</v>
+        <v>7018401</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120290801</v>
+        <v>120290803</v>
       </c>
       <c r="B6" t="n">
-        <v>79658</v>
+        <v>79527</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564059</v>
+        <v>564046</v>
       </c>
       <c r="R6" t="n">
-        <v>7018401</v>
+        <v>7018479</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120290803</v>
+        <v>120290802</v>
       </c>
       <c r="B7" t="n">
-        <v>79527</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564046</v>
+        <v>564039</v>
       </c>
       <c r="R7" t="n">
-        <v>7018479</v>
+        <v>7018489</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120290799</v>
+        <v>120290798</v>
       </c>
       <c r="B8" t="n">
-        <v>90598</v>
+        <v>79589</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>229748</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564051</v>
+        <v>563983</v>
       </c>
       <c r="R8" t="n">
-        <v>7018386</v>
+        <v>7018470</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120290795</v>
+        <v>120290797</v>
       </c>
       <c r="B9" t="n">
-        <v>90591</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563877</v>
+        <v>563965</v>
       </c>
       <c r="R9" t="n">
-        <v>7018280</v>
+        <v>7018323</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120290800</v>
+        <v>120290799</v>
       </c>
       <c r="B10" t="n">
-        <v>91023</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564059</v>
+        <v>564051</v>
       </c>
       <c r="R10" t="n">
-        <v>7018401</v>
+        <v>7018386</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45008-2023 artfynd.xlsx
+++ b/artfynd/A 45008-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120290795</v>
+        <v>120290799</v>
       </c>
       <c r="B2" t="n">
-        <v>90591</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563877</v>
+        <v>564051</v>
       </c>
       <c r="R2" t="n">
-        <v>7018280</v>
+        <v>7018386</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120290796</v>
+        <v>120290797</v>
       </c>
       <c r="B3" t="n">
-        <v>79489</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563924</v>
+        <v>563965</v>
       </c>
       <c r="R3" t="n">
-        <v>7018428</v>
+        <v>7018323</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120290800</v>
+        <v>120290795</v>
       </c>
       <c r="B4" t="n">
-        <v>91023</v>
+        <v>90591</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564059</v>
+        <v>563877</v>
       </c>
       <c r="R4" t="n">
-        <v>7018401</v>
+        <v>7018280</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120290801</v>
+        <v>120290802</v>
       </c>
       <c r="B5" t="n">
-        <v>79658</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564059</v>
+        <v>564039</v>
       </c>
       <c r="R5" t="n">
-        <v>7018401</v>
+        <v>7018489</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120290803</v>
+        <v>120290801</v>
       </c>
       <c r="B6" t="n">
-        <v>79527</v>
+        <v>79658</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564046</v>
+        <v>564059</v>
       </c>
       <c r="R6" t="n">
-        <v>7018479</v>
+        <v>7018401</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120290802</v>
+        <v>120290800</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>91023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564039</v>
+        <v>564059</v>
       </c>
       <c r="R7" t="n">
-        <v>7018489</v>
+        <v>7018401</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120290798</v>
+        <v>120290803</v>
       </c>
       <c r="B8" t="n">
-        <v>79589</v>
+        <v>79527</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229748</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563983</v>
+        <v>564046</v>
       </c>
       <c r="R8" t="n">
-        <v>7018470</v>
+        <v>7018479</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120290797</v>
+        <v>120290798</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>79589</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563965</v>
+        <v>563983</v>
       </c>
       <c r="R9" t="n">
-        <v>7018323</v>
+        <v>7018470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120290799</v>
+        <v>120290796</v>
       </c>
       <c r="B10" t="n">
-        <v>90598</v>
+        <v>79489</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>388</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564051</v>
+        <v>563924</v>
       </c>
       <c r="R10" t="n">
-        <v>7018386</v>
+        <v>7018428</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45008-2023 artfynd.xlsx
+++ b/artfynd/A 45008-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120290799</v>
+        <v>120290795</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
+        <v>90591</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564051</v>
+        <v>563877</v>
       </c>
       <c r="R2" t="n">
-        <v>7018386</v>
+        <v>7018280</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120290797</v>
+        <v>120290798</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>79589</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563965</v>
+        <v>563983</v>
       </c>
       <c r="R3" t="n">
-        <v>7018323</v>
+        <v>7018470</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120290795</v>
+        <v>120290796</v>
       </c>
       <c r="B4" t="n">
-        <v>90591</v>
+        <v>79489</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>388</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563877</v>
+        <v>563924</v>
       </c>
       <c r="R4" t="n">
-        <v>7018280</v>
+        <v>7018428</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120290802</v>
+        <v>120290797</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564039</v>
+        <v>563965</v>
       </c>
       <c r="R5" t="n">
-        <v>7018489</v>
+        <v>7018323</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120290801</v>
+        <v>120290799</v>
       </c>
       <c r="B6" t="n">
-        <v>79658</v>
+        <v>90598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564059</v>
+        <v>564051</v>
       </c>
       <c r="R6" t="n">
-        <v>7018401</v>
+        <v>7018386</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120290800</v>
+        <v>120290801</v>
       </c>
       <c r="B7" t="n">
-        <v>91023</v>
+        <v>79658</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120290803</v>
+        <v>120290802</v>
       </c>
       <c r="B8" t="n">
-        <v>79527</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564046</v>
+        <v>564039</v>
       </c>
       <c r="R8" t="n">
-        <v>7018479</v>
+        <v>7018489</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120290798</v>
+        <v>120290800</v>
       </c>
       <c r="B9" t="n">
-        <v>79589</v>
+        <v>91023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229748</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563983</v>
+        <v>564059</v>
       </c>
       <c r="R9" t="n">
-        <v>7018470</v>
+        <v>7018401</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120290796</v>
+        <v>120290803</v>
       </c>
       <c r="B10" t="n">
-        <v>79489</v>
+        <v>79527</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>388</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563924</v>
+        <v>564046</v>
       </c>
       <c r="R10" t="n">
-        <v>7018428</v>
+        <v>7018479</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 45008-2023 artfynd.xlsx
+++ b/artfynd/A 45008-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120290795</v>
+        <v>120290801</v>
       </c>
       <c r="B2" t="n">
-        <v>90591</v>
+        <v>79658</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563877</v>
+        <v>564059</v>
       </c>
       <c r="R2" t="n">
-        <v>7018280</v>
+        <v>7018401</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120290798</v>
+        <v>120290799</v>
       </c>
       <c r="B3" t="n">
-        <v>79589</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229748</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563983</v>
+        <v>564051</v>
       </c>
       <c r="R3" t="n">
-        <v>7018470</v>
+        <v>7018386</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120290796</v>
+        <v>120290797</v>
       </c>
       <c r="B4" t="n">
-        <v>79489</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563924</v>
+        <v>563965</v>
       </c>
       <c r="R4" t="n">
-        <v>7018428</v>
+        <v>7018323</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120290797</v>
+        <v>120290795</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>90591</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563965</v>
+        <v>563877</v>
       </c>
       <c r="R5" t="n">
-        <v>7018323</v>
+        <v>7018280</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120290799</v>
+        <v>120290800</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
+        <v>91023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564051</v>
+        <v>564059</v>
       </c>
       <c r="R6" t="n">
-        <v>7018386</v>
+        <v>7018401</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120290801</v>
+        <v>120290798</v>
       </c>
       <c r="B7" t="n">
-        <v>79658</v>
+        <v>79589</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>229748</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564059</v>
+        <v>563983</v>
       </c>
       <c r="R7" t="n">
-        <v>7018401</v>
+        <v>7018470</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120290802</v>
+        <v>120290796</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>79489</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564039</v>
+        <v>563924</v>
       </c>
       <c r="R8" t="n">
-        <v>7018489</v>
+        <v>7018428</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120290800</v>
+        <v>120290803</v>
       </c>
       <c r="B9" t="n">
-        <v>91023</v>
+        <v>79527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564059</v>
+        <v>564046</v>
       </c>
       <c r="R9" t="n">
-        <v>7018401</v>
+        <v>7018479</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120290803</v>
+        <v>120290802</v>
       </c>
       <c r="B10" t="n">
-        <v>79527</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564046</v>
+        <v>564039</v>
       </c>
       <c r="R10" t="n">
-        <v>7018479</v>
+        <v>7018489</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
